--- a/confirmation_forms/028_employment_confirmation_form--confirmation_forms.xlsx
+++ b/confirmation_forms/028_employment_confirmation_form--confirmation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -827,8 +827,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -856,12 +856,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'terminated'}</t>
+          <t>terminated</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Terminated'}</t>
+          <t>Terminated</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'temporary'}</t>
+          <t>temporary</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Temporary'}</t>
+          <t>Temporary</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'eligible'}</t>
+          <t>eligible</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Eligible'}</t>
+          <t>Eligible</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'ineligible'}</t>
+          <t>ineligible</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Ineligible'}</t>
+          <t>Ineligible</t>
         </is>
       </c>
     </row>
